--- a/public/templates/process-docs/低压交流电缆隐蔽工程质量验收记录.xlsx
+++ b/public/templates/process-docs/低压交流电缆隐蔽工程质量验收记录.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">编号：</t>
   </si>
   <si>
-    <t xml:space="preserve">5028G01-SG-ZHHC-AZ-001</t>
+    <t xml:space="preserve">{{文件编号}}</t>
   </si>
   <si>
     <t xml:space="preserve">工程名称</t>
@@ -128,13 +128,13 @@
     <t xml:space="preserve">施工单位</t>
   </si>
   <si>
-    <t xml:space="preserve">中核华辰建筑工程有限公司</t>
+    <t xml:space="preserve">{{施工单位}}</t>
   </si>
   <si>
     <t xml:space="preserve">项目经理</t>
   </si>
   <si>
-    <t xml:space="preserve">谢智敏</t>
+    <t xml:space="preserve">{{施工单位项目负责人}}</t>
   </si>
   <si>
     <t xml:space="preserve">专业工长</t>
@@ -143,13 +143,13 @@
     <t xml:space="preserve">分包单位</t>
   </si>
   <si>
-    <t xml:space="preserve">河南誉华美建设工程有限公司</t>
+    <t xml:space="preserve">{{分包单位}}</t>
   </si>
   <si>
     <t xml:space="preserve">分包负责人</t>
   </si>
   <si>
-    <t xml:space="preserve">胡彦芳</t>
+    <t xml:space="preserve">{{分包单位项目负责人}}</t>
   </si>
   <si>
     <t xml:space="preserve">席桂华</t>
@@ -546,7 +546,7 @@
     <t xml:space="preserve">钢筋</t>
   </si>
   <si>
-    <t xml:space="preserve">5028G01-SG-ZHHC-TJ-002</t>
+    <t xml:space="preserve">{{文件编号}}</t>
   </si>
   <si>
     <t xml:space="preserve">地基与基础</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">低压交流电缆</t>
   </si>
   <si>
-    <t xml:space="preserve">5028G01-SG-ZHHC-03-06-04-YB-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">刘彦堂</t>
+    <t xml:space="preserve">{{文件编号}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{施工单位项目技术负责人}}</t>
   </si>
   <si>
     <t xml:space="preserve">子方阵电气线路安装</t>
